--- a/artfynd/A 34740-2024 artfynd.xlsx
+++ b/artfynd/A 34740-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120122100</v>
+        <v>120121247</v>
       </c>
       <c r="B2" t="n">
         <v>96862</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334383</v>
+        <v>334326</v>
       </c>
       <c r="R2" t="n">
-        <v>6383705</v>
+        <v>6383708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stort område (ca 40m slinga) med revlummer</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120121247</v>
+        <v>120122100</v>
       </c>
       <c r="B3" t="n">
         <v>96862</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334326</v>
+        <v>334383</v>
       </c>
       <c r="R3" t="n">
-        <v>6383708</v>
+        <v>6383705</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stort område (ca 40m slinga) med revlummer</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34740-2024 artfynd.xlsx
+++ b/artfynd/A 34740-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120121247</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>96885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>120122100</v>
       </c>
       <c r="B3" t="n">
-        <v>96862</v>
+        <v>96885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34740-2024 artfynd.xlsx
+++ b/artfynd/A 34740-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120121247</v>
+        <v>120122100</v>
       </c>
       <c r="B2" t="n">
         <v>96885</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334326</v>
+        <v>334383</v>
       </c>
       <c r="R2" t="n">
-        <v>6383708</v>
+        <v>6383705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stort område (ca 40m slinga) med revlummer</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120122100</v>
+        <v>120121247</v>
       </c>
       <c r="B3" t="n">
         <v>96885</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334383</v>
+        <v>334326</v>
       </c>
       <c r="R3" t="n">
-        <v>6383705</v>
+        <v>6383708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stort område (ca 40m slinga) med revlummer</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34740-2024 artfynd.xlsx
+++ b/artfynd/A 34740-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120122100</v>
+        <v>120121247</v>
       </c>
       <c r="B2" t="n">
         <v>96885</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334383</v>
+        <v>334326</v>
       </c>
       <c r="R2" t="n">
-        <v>6383705</v>
+        <v>6383708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stort område (ca 40m slinga) med revlummer</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120121247</v>
+        <v>120122100</v>
       </c>
       <c r="B3" t="n">
         <v>96885</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334326</v>
+        <v>334383</v>
       </c>
       <c r="R3" t="n">
-        <v>6383708</v>
+        <v>6383705</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stort område (ca 40m slinga) med revlummer</t>
         </is>
       </c>
       <c r="AD3" t="b">
